--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:30</t>
+          <t>2026-10-14 14:14:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-DatasetSeriesShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:48</t>
+          <t>2026-10-14 14:30:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#DatasetSeriesShape</t>
+          <t>http://data.health-ri.nl/core/p2/DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dcatap:applicableLegislation</t>
+          <t>hrishapes:DatasetSeriesShape#dcatap:applicableLegislation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1742,12 +1759,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dcat:contactPoint</t>
+          <t>hrishapes:DatasetSeriesShape#dcat:contactPoint</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1800,12 +1817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:description</t>
+          <t>hrishapes:DatasetSeriesShape#dct:description</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1862,12 +1879,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:accrualPeriodicity</t>
+          <t>hrishapes:DatasetSeriesShape#dct:accrualPeriodicity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1922,12 +1939,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:spatial</t>
+          <t>hrishapes:DatasetSeriesShape#dct:spatial</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1980,12 +1997,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:modified</t>
+          <t>hrishapes:DatasetSeriesShape#dct:modified</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2048,12 +2065,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:publisher</t>
+          <t>hrishapes:DatasetSeriesShape#dct:publisher</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2108,12 +2125,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:issued</t>
+          <t>hrishapes:DatasetSeriesShape#dct:issued</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2176,12 +2193,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:temporal</t>
+          <t>hrishapes:DatasetSeriesShape#dct:temporal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2234,12 +2251,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape/dct:title</t>
+          <t>hrishapes:DatasetSeriesShape#dct:title</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hri:DatasetSeriesShape</t>
+          <t>hrishapes:DatasetSeriesShape</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:38</t>
+          <t>2026-10-19 15:50:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#KindShape</t>
+          <t>http://data.health-ri.nl/core/p2/KindShape</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2097,7 +2097,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#PeriodOfTimeShape</t>
+          <t>http://data.health-ri.nl/core/p2/PeriodOfTimeShape</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:03</t>
+          <t>2026-10-26 13:15:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:50</t>
+          <t>2026-10-26 16:19:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:38</t>
+          <t>2026-10-27 15:44:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:13</t>
+          <t>2026-10-28 09:50:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:42</t>
+          <t>2026-10-28 11:04:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
